--- a/2026/YRIGOYEN 7630/Febrero/YRIGOYEN7630-Febrero.xlsx
+++ b/2026/YRIGOYEN 7630/Febrero/YRIGOYEN7630-Febrero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC44A0F0-90D9-440A-9E65-12FAFF611666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE5E9F3-CDD0-4399-8A00-37ABC53FCC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -118,9 +118,6 @@
     <t>HORARIOS DE ATENCION: LUNES A VIERNES</t>
   </si>
   <si>
-    <t>10 A 16HS - EMERGENCIAS 24HS</t>
-  </si>
-  <si>
     <t>Deuda o Saldo a favor</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>Dice que abono $264.419,03 el 30/12 y que no le pusimos pago, adjunta su comprobante - Debe abonar $374.804,03.</t>
+  </si>
+  <si>
+    <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
 </sst>
 </file>
@@ -1367,81 +1367,6 @@
     <xf numFmtId="44" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1450,6 +1375,81 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="21" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1833,7 +1833,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
@@ -1851,7 +1851,7 @@
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
       <c r="B3" s="198" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="198"/>
       <c r="D3" s="198"/>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="100" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1883,18 +1883,18 @@
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="201" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="201"/>
     </row>
@@ -1909,7 +1909,7 @@
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="200" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="200"/>
       <c r="C13" s="200"/>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="59"/>
       <c r="C24" s="59"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="59"/>
       <c r="C30" s="59"/>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="196" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B33" s="197"/>
       <c r="C33" s="54"/>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="178" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="179"/>
       <c r="C34" s="54"/>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="196" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="197"/>
       <c r="C35" s="54"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E35" s="145"/>
       <c r="H35" s="156" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2114,7 +2114,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -2122,22 +2122,22 @@
       <c r="E37" s="147"/>
     </row>
     <row r="38" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="194" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" s="195"/>
+      <c r="A38" s="202" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="203"/>
       <c r="C38" s="56"/>
       <c r="D38" s="182">
         <f>6696+26570</f>
         <v>33266</v>
       </c>
       <c r="E38" s="180" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="196" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B39" s="197"/>
       <c r="C39" s="56"/>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="54"/>
@@ -2180,13 +2180,13 @@
         <v>937097.26</v>
       </c>
       <c r="E42" s="159" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" s="126"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="54"/>
@@ -2194,12 +2194,12 @@
         <v>10602.27</v>
       </c>
       <c r="E43" s="159" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="54"/>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2226,7 +2226,7 @@
         <v>132242.74</v>
       </c>
       <c r="E45" s="159" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -2282,7 +2282,7 @@
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2290,12 +2290,12 @@
         <v>81386.33</v>
       </c>
       <c r="E50" s="159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B51" s="162"/>
       <c r="C51" s="5"/>
@@ -2303,12 +2303,12 @@
         <v>38806.65</v>
       </c>
       <c r="E51" s="159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2316,20 +2316,20 @@
         <v>26145.55</v>
       </c>
       <c r="E52" s="159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="194" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="195"/>
+      <c r="A53" s="202" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="203"/>
       <c r="C53" s="5"/>
       <c r="D53" s="162">
         <v>377536.65</v>
       </c>
       <c r="E53" s="159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2353,7 +2353,7 @@
     </row>
     <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="164" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B56" s="157"/>
       <c r="C56" s="5"/>
@@ -2361,12 +2361,12 @@
         <v>85000</v>
       </c>
       <c r="E56" s="163" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="164" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" s="157"/>
       <c r="C57" s="5"/>
@@ -2374,12 +2374,12 @@
         <v>45000</v>
       </c>
       <c r="E57" s="163" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="164" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B58" s="157"/>
       <c r="C58" s="5"/>
@@ -2387,12 +2387,12 @@
         <v>340000</v>
       </c>
       <c r="E58" s="185" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="164" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B59" s="157"/>
       <c r="C59" s="5"/>
@@ -2400,33 +2400,33 @@
         <v>59600</v>
       </c>
       <c r="E59" s="163" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="194" t="s">
-        <v>111</v>
-      </c>
-      <c r="B60" s="195"/>
+      <c r="A60" s="202" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="203"/>
       <c r="C60" s="5"/>
       <c r="D60" s="108">
         <v>35500</v>
       </c>
       <c r="E60" s="163" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="194" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" s="195"/>
+      <c r="A61" s="202" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="203"/>
       <c r="C61" s="5"/>
       <c r="D61" s="108">
         <v>45000</v>
       </c>
       <c r="E61" s="163" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2452,7 +2452,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="13"/>
@@ -2549,15 +2549,15 @@
       <c r="E73" s="120"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="194"/>
-      <c r="B74" s="195"/>
+      <c r="A74" s="202"/>
+      <c r="B74" s="203"/>
       <c r="C74" s="5"/>
       <c r="D74" s="130"/>
       <c r="E74" s="106"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="194"/>
-      <c r="B75" s="195"/>
+      <c r="A75" s="202"/>
+      <c r="B75" s="203"/>
       <c r="C75" s="5"/>
       <c r="D75" s="108"/>
       <c r="E75" s="106"/>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="101" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B88" s="102">
         <f>E83</f>
@@ -2650,29 +2650,29 @@
     <row r="89" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="192"/>
-      <c r="B91" s="192"/>
-      <c r="C91" s="192"/>
-      <c r="D91" s="192"/>
-      <c r="E91" s="192"/>
+      <c r="A91" s="204"/>
+      <c r="B91" s="204"/>
+      <c r="C91" s="204"/>
+      <c r="D91" s="204"/>
+      <c r="E91" s="204"/>
     </row>
     <row r="92" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="192"/>
-      <c r="B92" s="192"/>
-      <c r="C92" s="192"/>
-      <c r="D92" s="192"/>
-      <c r="E92" s="192"/>
+      <c r="A92" s="204"/>
+      <c r="B92" s="204"/>
+      <c r="C92" s="204"/>
+      <c r="D92" s="204"/>
+      <c r="E92" s="204"/>
     </row>
     <row r="93" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="192"/>
-      <c r="B93" s="192"/>
-      <c r="C93" s="192"/>
-      <c r="D93" s="192"/>
-      <c r="E93" s="192"/>
+      <c r="A93" s="204"/>
+      <c r="B93" s="204"/>
+      <c r="C93" s="204"/>
+      <c r="D93" s="204"/>
+      <c r="E93" s="204"/>
     </row>
     <row r="95" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" s="127"/>
       <c r="C95" s="24"/>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B99" s="110">
         <f>B120</f>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="125" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B101" s="49"/>
       <c r="C101" s="24"/>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="108" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="133" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B108" s="134">
         <v>-864378.73609999567</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B109" s="139">
         <f>-B86</f>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B110" s="139">
         <f>-B87</f>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B111" s="139">
         <f>B120</f>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B112" s="140">
         <f>PRORRATEO!F29</f>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="113" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="137" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B113" s="138">
         <f>SUM(B108:C112)</f>
@@ -2831,16 +2831,16 @@
     </row>
     <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="193" t="s">
-        <v>33</v>
-      </c>
-      <c r="B116" s="193"/>
-      <c r="C116" s="193"/>
+      <c r="A116" s="205" t="s">
+        <v>32</v>
+      </c>
+      <c r="B116" s="205"/>
+      <c r="C116" s="205"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="193"/>
-      <c r="B117" s="193"/>
-      <c r="C117" s="193"/>
+      <c r="A117" s="205"/>
+      <c r="B117" s="205"/>
+      <c r="C117" s="205"/>
     </row>
     <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="122"/>
@@ -2870,51 +2870,51 @@
       <c r="M121" s="8"/>
     </row>
     <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="192"/>
-      <c r="B122" s="192"/>
-      <c r="C122" s="192"/>
-      <c r="D122" s="192"/>
-      <c r="E122" s="192"/>
+      <c r="A122" s="204"/>
+      <c r="B122" s="204"/>
+      <c r="C122" s="204"/>
+      <c r="D122" s="204"/>
+      <c r="E122" s="204"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="192"/>
-      <c r="B123" s="192"/>
-      <c r="C123" s="192"/>
-      <c r="D123" s="192"/>
-      <c r="E123" s="192"/>
+      <c r="A123" s="204"/>
+      <c r="B123" s="204"/>
+      <c r="C123" s="204"/>
+      <c r="D123" s="204"/>
+      <c r="E123" s="204"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="192"/>
-      <c r="B124" s="192"/>
-      <c r="C124" s="192"/>
-      <c r="D124" s="192"/>
-      <c r="E124" s="192"/>
+      <c r="A124" s="204"/>
+      <c r="B124" s="204"/>
+      <c r="C124" s="204"/>
+      <c r="D124" s="204"/>
+      <c r="E124" s="204"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125" s="192"/>
-      <c r="B125" s="192"/>
-      <c r="C125" s="192"/>
-      <c r="D125" s="192"/>
-      <c r="E125" s="192"/>
+      <c r="A125" s="204"/>
+      <c r="B125" s="204"/>
+      <c r="C125" s="204"/>
+      <c r="D125" s="204"/>
+      <c r="E125" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A122:E125"/>
     <mergeCell ref="A116:C117"/>
     <mergeCell ref="A91:E93"/>
     <mergeCell ref="A75:B75"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2950,15 +2950,15 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
@@ -2967,7 +2967,7 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="165">
@@ -2977,7 +2977,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
       <c r="J2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="132">
@@ -3004,77 +3004,77 @@
       <c r="N3" s="62"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="204" t="s">
+      <c r="A4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="211" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="211" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="208" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="204" t="s">
+      <c r="E4" s="207" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="212" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="208" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="208" t="s">
+      <c r="G4" s="213" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="207" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="207" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="208" t="s">
+      <c r="J4" s="207" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="215" t="s">
-        <v>82</v>
+      <c r="K4" s="216" t="s">
+        <v>81</v>
       </c>
       <c r="L4" s="65" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" s="210" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="209" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="202" t="s">
-        <v>37</v>
+      <c r="N4" s="218" t="s">
+        <v>36</v>
       </c>
       <c r="Q4" s="132">
         <v>3774269.17</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="206"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="216"/>
+      <c r="A5" s="212"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="217"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="M5" s="211"/>
-      <c r="N5" s="203"/>
+      <c r="M5" s="210"/>
+      <c r="N5" s="219"/>
     </row>
     <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66">
         <v>1</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="66"/>
       <c r="D6" s="75">
@@ -3128,7 +3128,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="75">
@@ -3179,21 +3179,21 @@
       <c r="P7" s="45"/>
     </row>
     <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="217">
+      <c r="A8" s="192">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="217" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="218"/>
-      <c r="D8" s="219">
+      <c r="B8" s="192" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="193"/>
+      <c r="D8" s="194">
         <v>6.65</v>
       </c>
-      <c r="E8" s="220">
+      <c r="E8" s="195">
         <v>536769.03</v>
       </c>
-      <c r="F8" s="220">
+      <c r="F8" s="195">
         <v>150000.03</v>
       </c>
       <c r="G8" s="78">
@@ -3238,7 +3238,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="75">
@@ -3294,7 +3294,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="75">
@@ -3347,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="75">
@@ -3402,7 +3402,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="75">
@@ -3454,7 +3454,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="75">
@@ -3503,7 +3503,7 @@
         <v>0.08</v>
       </c>
       <c r="Q13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -3512,7 +3512,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="75">
@@ -3567,7 +3567,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="75">
@@ -3622,7 +3622,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="67"/>
       <c r="D16" s="75">
@@ -3677,7 +3677,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="67"/>
       <c r="D17" s="75">
@@ -3732,7 +3732,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" s="67"/>
       <c r="D18" s="75">
@@ -3787,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="67"/>
       <c r="D19" s="75">
@@ -3839,7 +3839,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="186" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C20" s="187"/>
       <c r="D20" s="188">
@@ -3894,7 +3894,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="75">
@@ -3950,7 +3950,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="75">
@@ -4004,7 +4004,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="131"/>
       <c r="D23" s="75">
@@ -4196,88 +4196,94 @@
     </row>
     <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="192" t="str">
+      <c r="B32" s="204" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="192"/>
-      <c r="D32" s="192"/>
-      <c r="E32" s="192"/>
-      <c r="F32" s="192"/>
-      <c r="G32" s="192"/>
-      <c r="H32" s="192"/>
-      <c r="I32" s="192"/>
-      <c r="J32" s="192"/>
-      <c r="K32" s="192"/>
-      <c r="L32" s="192"/>
+      <c r="C32" s="204"/>
+      <c r="D32" s="204"/>
+      <c r="E32" s="204"/>
+      <c r="F32" s="204"/>
+      <c r="G32" s="204"/>
+      <c r="H32" s="204"/>
+      <c r="I32" s="204"/>
+      <c r="J32" s="204"/>
+      <c r="K32" s="204"/>
+      <c r="L32" s="204"/>
     </row>
     <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="192"/>
-      <c r="C33" s="192"/>
-      <c r="D33" s="192"/>
-      <c r="E33" s="192"/>
-      <c r="F33" s="192"/>
-      <c r="G33" s="192"/>
-      <c r="H33" s="192"/>
-      <c r="I33" s="192"/>
-      <c r="J33" s="192"/>
-      <c r="K33" s="192"/>
-      <c r="L33" s="192"/>
+      <c r="B33" s="204"/>
+      <c r="C33" s="204"/>
+      <c r="D33" s="204"/>
+      <c r="E33" s="204"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="204"/>
+      <c r="H33" s="204"/>
+      <c r="I33" s="204"/>
+      <c r="J33" s="204"/>
+      <c r="K33" s="204"/>
+      <c r="L33" s="204"/>
     </row>
     <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="192"/>
-      <c r="C34" s="192"/>
-      <c r="D34" s="192"/>
-      <c r="E34" s="192"/>
-      <c r="F34" s="192"/>
-      <c r="G34" s="192"/>
-      <c r="H34" s="192"/>
-      <c r="I34" s="192"/>
-      <c r="J34" s="192"/>
-      <c r="K34" s="192"/>
-      <c r="L34" s="192"/>
+      <c r="B34" s="204"/>
+      <c r="C34" s="204"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="204"/>
+      <c r="F34" s="204"/>
+      <c r="G34" s="204"/>
+      <c r="H34" s="204"/>
+      <c r="I34" s="204"/>
+      <c r="J34" s="204"/>
+      <c r="K34" s="204"/>
+      <c r="L34" s="204"/>
     </row>
     <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="192"/>
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
-      <c r="E35" s="192"/>
-      <c r="F35" s="192"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
-      <c r="I35" s="192"/>
-      <c r="J35" s="192"/>
-      <c r="K35" s="192"/>
-      <c r="L35" s="192"/>
+      <c r="B35" s="204"/>
+      <c r="C35" s="204"/>
+      <c r="D35" s="204"/>
+      <c r="E35" s="204"/>
+      <c r="F35" s="204"/>
+      <c r="G35" s="204"/>
+      <c r="H35" s="204"/>
+      <c r="I35" s="204"/>
+      <c r="J35" s="204"/>
+      <c r="K35" s="204"/>
+      <c r="L35" s="204"/>
     </row>
     <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="192"/>
-      <c r="C36" s="192"/>
-      <c r="D36" s="192"/>
-      <c r="E36" s="192"/>
-      <c r="F36" s="192"/>
-      <c r="G36" s="192"/>
-      <c r="H36" s="192"/>
-      <c r="I36" s="192"/>
-      <c r="J36" s="192"/>
-      <c r="K36" s="192"/>
-      <c r="L36" s="192"/>
+      <c r="B36" s="204"/>
+      <c r="C36" s="204"/>
+      <c r="D36" s="204"/>
+      <c r="E36" s="204"/>
+      <c r="F36" s="204"/>
+      <c r="G36" s="204"/>
+      <c r="H36" s="204"/>
+      <c r="I36" s="204"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="204"/>
+      <c r="L36" s="204"/>
     </row>
     <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="192"/>
-      <c r="C37" s="192"/>
-      <c r="D37" s="192"/>
-      <c r="E37" s="192"/>
-      <c r="F37" s="192"/>
-      <c r="G37" s="192"/>
-      <c r="H37" s="192"/>
-      <c r="I37" s="192"/>
-      <c r="J37" s="192"/>
-      <c r="K37" s="192"/>
-      <c r="L37" s="192"/>
+      <c r="B37" s="204"/>
+      <c r="C37" s="204"/>
+      <c r="D37" s="204"/>
+      <c r="E37" s="204"/>
+      <c r="F37" s="204"/>
+      <c r="G37" s="204"/>
+      <c r="H37" s="204"/>
+      <c r="I37" s="204"/>
+      <c r="J37" s="204"/>
+      <c r="K37" s="204"/>
+      <c r="L37" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
@@ -4287,12 +4293,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4306,7 +4306,7 @@
   <sheetData>
     <row r="5" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C5" s="190" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" s="191"/>
       <c r="E5" s="191"/>
@@ -4315,7 +4315,7 @@
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C8" s="156" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" s="156"/>
       <c r="E8" s="156"/>

--- a/2026/YRIGOYEN 7630/Febrero/YRIGOYEN7630-Febrero.xlsx
+++ b/2026/YRIGOYEN 7630/Febrero/YRIGOYEN7630-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\YRIGOYEN 7630\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA7EA58-C66A-49BF-B564-816FDBF8F155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7978A702-DAA2-4629-BB8F-E71FC5F47F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -21,25 +21,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$121</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="118">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -327,12 +314,6 @@
     <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE YRIGOYEN 7630</t>
   </si>
   <si>
-    <t>Le pusimos plata demas en enero 2026 a esta Sra.</t>
-  </si>
-  <si>
-    <t>Dice que abono $264.419,03 el 30/12 y que no le pusimos pago, adjunta su comprobante - Debe abonar $374.804,03.</t>
-  </si>
-  <si>
     <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
   <si>
@@ -397,6 +378,9 @@
   </si>
   <si>
     <t>Punitorios mal cobrados UF 5</t>
+  </si>
+  <si>
+    <t>El departamento 7 adjunta un monton de comprobantes desde el mail de (mer_paisa@hotmail.com) antiguos para que reveamos su deuda. Chequear y revisar.</t>
   </si>
 </sst>
 </file>
@@ -404,14 +388,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -612,7 +596,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -681,12 +665,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1100,8 +1078,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="216">
@@ -1112,7 +1090,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1127,9 +1105,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1144,7 +1122,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1154,39 +1132,39 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1200,7 +1178,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1208,117 +1186,117 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1326,95 +1304,18 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="16" fontId="23" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1422,37 +1323,114 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="20" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="20" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="3" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1815,21 +1793,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M125"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.6328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="70" t="s">
         <v>54</v>
@@ -1838,7 +1816,7 @@
       <c r="D1" s="70"/>
       <c r="E1" s="71"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="72" t="s">
         <v>28</v>
@@ -1847,16 +1825,16 @@
       <c r="D2" s="72"/>
       <c r="E2" s="73"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="175" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="176"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="190" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="191"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1867,12 +1845,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="72" t="s">
@@ -1880,68 +1858,68 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>94</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="178" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="178"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="178"/>
-      <c r="C9" s="178"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="178"/>
-      <c r="C10" s="178"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="177" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="193" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="193"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="193"/>
+      <c r="C9" s="193"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="193"/>
+      <c r="C10" s="193"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="177"/>
-      <c r="C13" s="177"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="177"/>
-      <c r="B14" s="177"/>
-      <c r="C14" s="177"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="177"/>
-      <c r="B15" s="177"/>
-      <c r="C15" s="177"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="177"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="177"/>
-      <c r="B16" s="177"/>
-      <c r="C16" s="177"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="177"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="192"/>
+      <c r="C13" s="192"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="192"/>
+      <c r="B14" s="192"/>
+      <c r="C14" s="192"/>
+      <c r="D14" s="192"/>
+      <c r="E14" s="192"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="192"/>
+      <c r="B15" s="192"/>
+      <c r="C15" s="192"/>
+      <c r="D15" s="192"/>
+      <c r="E15" s="192"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="192"/>
+      <c r="B16" s="192"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1950,7 +1928,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>34</v>
       </c>
@@ -1959,128 +1937,128 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="198">
+      <c r="D22" s="170">
         <v>1010153</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="198"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="58"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="199">
+      <c r="D24" s="171">
         <f>SUM(D22:D23)</f>
         <v>1010153</v>
       </c>
       <c r="E24" s="141"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="198"/>
+      <c r="D25" s="170"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="29"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="198"/>
+      <c r="D26" s="170"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="198"/>
+      <c r="D27" s="170"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="200"/>
+      <c r="D28" s="172"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="200"/>
+      <c r="D29" s="172"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="58" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="58"/>
       <c r="C30" s="58"/>
-      <c r="D30" s="201">
+      <c r="D30" s="173">
         <f>SUM(D25:D29)</f>
         <v>0</v>
       </c>
       <c r="E30" s="141"/>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
-      <c r="D31" s="202"/>
+      <c r="D31" s="174"/>
       <c r="E31" s="142">
         <f>D24+D30</f>
         <v>1010153</v>
       </c>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
-      <c r="D32" s="203"/>
+      <c r="D32" s="175"/>
       <c r="E32" s="143"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="173" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="174"/>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="188" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="189"/>
       <c r="C33" s="53"/>
-      <c r="D33" s="198">
+      <c r="D33" s="170">
         <v>45000</v>
       </c>
       <c r="E33" s="144"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="173" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="174"/>
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="188" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="189"/>
       <c r="C34" s="53"/>
-      <c r="D34" s="204">
+      <c r="D34" s="176">
         <v>147300</v>
       </c>
       <c r="E34" s="144"/>
@@ -2088,48 +2066,48 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
-      <c r="D35" s="205"/>
+      <c r="D35" s="177"/>
       <c r="E35" s="145">
         <f>SUM(D33:D34)</f>
         <v>192300</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="36" t="s">
         <v>31</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
-      <c r="D36" s="206"/>
+      <c r="D36" s="178"/>
       <c r="E36" s="146"/>
     </row>
-    <row r="37" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="171" t="s">
+    <row r="37" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="194" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="172"/>
+      <c r="B37" s="195"/>
       <c r="C37" s="55"/>
-      <c r="D37" s="207">
+      <c r="D37" s="179">
         <f>26570+6696</f>
         <v>33266</v>
       </c>
       <c r="E37" s="165" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="173" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="188" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="174"/>
+      <c r="B38" s="189"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="208">
+      <c r="D38" s="180">
         <v>54278</v>
       </c>
       <c r="E38" s="147" t="str">
@@ -2137,28 +2115,28 @@
         <v>Debito 03/02</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
-      <c r="D39" s="205"/>
+      <c r="D39" s="177"/>
       <c r="E39" s="148">
         <f>SUM(D37:D38)</f>
         <v>87544</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B40" s="149"/>
       <c r="C40" s="149"/>
-      <c r="D40" s="209"/>
+      <c r="D40" s="181"/>
       <c r="E40" s="150"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>47</v>
       </c>
@@ -2168,11 +2146,11 @@
         <v>634417.24</v>
       </c>
       <c r="E41" s="156" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G41" s="125"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>77</v>
       </c>
@@ -2182,10 +2160,10 @@
         <v>10602.27</v>
       </c>
       <c r="E42" s="156" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>77</v>
       </c>
@@ -2204,27 +2182,27 @@
       </c>
       <c r="G43" s="140"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="210">
+      <c r="D44" s="182">
         <v>118480.73</v>
       </c>
       <c r="E44" s="156" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de FEBRERO</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="210">
+      <c r="D45" s="182">
         <v>5792.98</v>
       </c>
       <c r="E45" s="157" t="str">
@@ -2232,14 +2210,14 @@
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de FEBRERO</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="210">
+      <c r="D46" s="182">
         <v>52136.85</v>
       </c>
       <c r="E46" s="158" t="str">
@@ -2247,175 +2225,175 @@
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="30" t="s">
         <v>3</v>
       </c>
       <c r="B47" s="149"/>
       <c r="C47" s="149"/>
-      <c r="D47" s="211"/>
+      <c r="D47" s="183"/>
       <c r="E47" s="148">
         <f>SUM(D41:D46)</f>
         <v>896962.36</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B48" s="149"/>
       <c r="C48" s="149"/>
-      <c r="D48" s="209"/>
+      <c r="D48" s="181"/>
       <c r="E48" s="150"/>
     </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="210">
+      <c r="D49" s="182">
         <f>138668.19-76476.33</f>
         <v>62191.86</v>
       </c>
       <c r="E49" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B50" s="159"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="210">
+      <c r="D50" s="182">
         <f>74636.75-33896.65</f>
         <v>40740.1</v>
       </c>
       <c r="E50" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="210">
+      <c r="D51" s="182">
         <v>26185.98</v>
       </c>
       <c r="E51" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="171" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="194" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="172"/>
+      <c r="B52" s="195"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="210">
+      <c r="D52" s="182">
         <v>372717.24</v>
       </c>
       <c r="E52" s="156" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30" t="s">
         <v>4</v>
       </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
-      <c r="D53" s="212"/>
+      <c r="D53" s="184"/>
       <c r="E53" s="148">
         <f>SUM(D49:D52)</f>
         <v>501835.18</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="36"/>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
-      <c r="D54" s="205"/>
+      <c r="D54" s="177"/>
       <c r="E54" s="151"/>
     </row>
-    <row r="55" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B55" s="155"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="210">
+      <c r="D55" s="182">
         <v>85000</v>
       </c>
       <c r="E55" s="160" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="161" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B56" s="155"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="210"/>
+      <c r="D56" s="182"/>
       <c r="E56" s="160"/>
     </row>
-    <row r="57" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="161" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B57" s="155"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="213">
+      <c r="D57" s="185">
         <v>340000</v>
       </c>
       <c r="E57" s="166" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="161" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B58" s="155"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="213">
+      <c r="D58" s="185">
         <v>85000</v>
       </c>
       <c r="E58" s="160" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="194" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" s="195"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="185">
+        <v>46200</v>
+      </c>
+      <c r="E59" s="160" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="194" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="171" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" s="172"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="213">
-        <v>46200</v>
-      </c>
-      <c r="E59" s="160" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="171" t="s">
-        <v>112</v>
-      </c>
-      <c r="B60" s="172"/>
+      <c r="B60" s="195"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="213">
+      <c r="D60" s="185">
         <v>78650</v>
       </c>
       <c r="E60" s="160" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="30" t="s">
         <v>9</v>
       </c>
@@ -2427,38 +2405,38 @@
         <v>634850</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="36" t="s">
         <v>12</v>
       </c>
       <c r="B62" s="68"/>
       <c r="C62" s="30"/>
-      <c r="D62" s="202"/>
+      <c r="D62" s="174"/>
       <c r="E62" s="151"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="210">
+      <c r="D63" s="182">
         <v>53000</v>
       </c>
       <c r="E63" s="153"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="210">
+      <c r="D64" s="182">
         <v>71779.02</v>
       </c>
       <c r="E64" s="41"/>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="52" t="s">
         <v>16</v>
       </c>
@@ -2470,14 +2448,14 @@
         <v>124779.02</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="103"/>
       <c r="E66" s="111"/>
     </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="31" t="s">
         <v>50</v>
       </c>
@@ -2486,13 +2464,13 @@
       <c r="D67" s="112"/>
       <c r="E67" s="113"/>
     </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="D68" s="114"/>
       <c r="E68" s="115"/>
       <c r="F68" s="44"/>
     </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
@@ -2511,7 +2489,7 @@
       <c r="K69" s="125"/>
       <c r="L69" s="125"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D70" s="114"/>
       <c r="E70" s="114"/>
       <c r="H70" s="125"/>
@@ -2520,12 +2498,12 @@
       <c r="K70" s="125"/>
       <c r="L70" s="125"/>
     </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D71" s="114"/>
       <c r="E71" s="114"/>
       <c r="H71" s="164"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
         <v>45</v>
       </c>
@@ -2534,35 +2512,35 @@
       <c r="D72" s="118"/>
       <c r="E72" s="119"/>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="171"/>
-      <c r="B73" s="172"/>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="194"/>
+      <c r="B73" s="195"/>
       <c r="C73" s="5"/>
       <c r="D73" s="129"/>
       <c r="E73" s="105"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A74" s="171"/>
-      <c r="B74" s="172"/>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="194"/>
+      <c r="B74" s="195"/>
       <c r="C74" s="5"/>
       <c r="D74" s="107"/>
       <c r="E74" s="105"/>
     </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="173"/>
-      <c r="B75" s="174"/>
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="188"/>
+      <c r="B75" s="189"/>
       <c r="C75" s="5"/>
       <c r="D75" s="107"/>
       <c r="E75" s="105"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="106"/>
       <c r="B76" s="108"/>
       <c r="C76" s="5"/>
       <c r="D76" s="107"/>
       <c r="E76" s="105"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="50"/>
       <c r="B77" s="49"/>
       <c r="C77" s="49"/>
@@ -2572,9 +2550,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="31" t="s">
         <v>20</v>
       </c>
@@ -2583,8 +2561,8 @@
       <c r="D80" s="32"/>
       <c r="E80" s="102"/>
     </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>21</v>
       </c>
@@ -2596,8 +2574,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="100" t="s">
         <v>14</v>
       </c>
@@ -2606,7 +2584,7 @@
         <v>3448423.56</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="100" t="s">
         <v>15</v>
       </c>
@@ -2615,7 +2593,7 @@
         <v>3448423.56</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="100" t="s">
         <v>22</v>
       </c>
@@ -2624,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="100" t="s">
         <v>40</v>
       </c>
@@ -2633,44 +2611,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="169"/>
-      <c r="B90" s="169"/>
-      <c r="C90" s="169"/>
-      <c r="D90" s="169"/>
-      <c r="E90" s="169"/>
-    </row>
-    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="169"/>
-      <c r="B91" s="169"/>
-      <c r="C91" s="169"/>
-      <c r="D91" s="169"/>
-      <c r="E91" s="169"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="169"/>
-      <c r="B92" s="169"/>
-      <c r="C92" s="169"/>
-      <c r="D92" s="169"/>
-      <c r="E92" s="169"/>
-    </row>
-    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="196"/>
+      <c r="B90" s="196"/>
+      <c r="C90" s="196"/>
+      <c r="D90" s="196"/>
+      <c r="E90" s="196"/>
+    </row>
+    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="196"/>
+      <c r="B91" s="196"/>
+      <c r="C91" s="196"/>
+      <c r="D91" s="196"/>
+      <c r="E91" s="196"/>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="196"/>
+      <c r="B92" s="196"/>
+      <c r="C92" s="196"/>
+      <c r="D92" s="196"/>
+      <c r="E92" s="196"/>
+    </row>
+    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B94" s="126"/>
       <c r="C94" s="24"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="34"/>
       <c r="B95" s="60">
         <v>0</v>
       </c>
       <c r="C95" s="26"/>
     </row>
-    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="25" t="s">
         <v>7</v>
       </c>
@@ -2680,14 +2658,14 @@
       </c>
       <c r="C96" s="24"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="25"/>
       <c r="B97" s="41">
         <v>0</v>
       </c>
       <c r="C97" s="24"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="25" t="s">
         <v>41</v>
       </c>
@@ -2697,19 +2675,19 @@
       </c>
       <c r="C98" s="24"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="28"/>
       <c r="B99" s="48"/>
       <c r="C99" s="24"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="124" t="s">
         <v>46</v>
       </c>
       <c r="B100" s="48"/>
       <c r="C100" s="24"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="40" t="s">
         <v>23</v>
       </c>
@@ -2719,7 +2697,7 @@
       </c>
       <c r="C101" s="24"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
         <v>24</v>
       </c>
@@ -2729,7 +2707,7 @@
       </c>
       <c r="C102" s="24"/>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="33" t="s">
         <v>9</v>
       </c>
@@ -2740,23 +2718,23 @@
       <c r="C103" s="27"/>
       <c r="D103" s="44"/>
     </row>
-    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="42"/>
       <c r="C104" s="27"/>
       <c r="D104" s="44"/>
       <c r="E104" s="127"/>
       <c r="F104" s="128"/>
     </row>
-    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="43"/>
       <c r="C105" s="27"/>
     </row>
-    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106"/>
       <c r="B106" s="42"/>
       <c r="C106" s="38"/>
     </row>
-    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="132" t="s">
         <v>85</v>
       </c>
@@ -2766,7 +2744,7 @@
       <c r="C107" s="38"/>
       <c r="D107" s="47"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="55" t="s">
         <v>51</v>
       </c>
@@ -2775,7 +2753,7 @@
         <v>-3448423.56</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="55" t="s">
         <v>52</v>
       </c>
@@ -2784,15 +2762,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="55" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B110" s="138">
         <v>-10670</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="55" t="s">
         <v>83</v>
       </c>
@@ -2801,7 +2779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="55" t="s">
         <v>53</v>
       </c>
@@ -2810,7 +2788,7 @@
         <v>3434868.8600000003</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="136" t="s">
         <v>48</v>
       </c>
@@ -2819,24 +2797,24 @@
         <v>-1433924.8360999953</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="134"/>
       <c r="B114" s="134"/>
     </row>
-    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A116" s="170" t="s">
+    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="197" t="s">
         <v>32</v>
       </c>
-      <c r="B116" s="170"/>
-      <c r="C116" s="170"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A117" s="170"/>
-      <c r="B117" s="170"/>
-      <c r="C117" s="170"/>
-    </row>
-    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="197"/>
+      <c r="C116" s="197"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="197"/>
+      <c r="B117" s="197"/>
+      <c r="C117" s="197"/>
+    </row>
+    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="121"/>
       <c r="B118" s="37"/>
       <c r="C118" s="37">
@@ -2844,13 +2822,13 @@
       </c>
       <c r="E118" s="140"/>
     </row>
-    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="121"/>
       <c r="B119" s="123"/>
       <c r="C119" s="120"/>
       <c r="D119" s="140"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="45" t="s">
         <v>9</v>
       </c>
@@ -2860,55 +2838,55 @@
       </c>
       <c r="C120" s="46"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M121" s="8"/>
     </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="169"/>
-      <c r="B122" s="169"/>
-      <c r="C122" s="169"/>
-      <c r="D122" s="169"/>
-      <c r="E122" s="169"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A123" s="169"/>
-      <c r="B123" s="169"/>
-      <c r="C123" s="169"/>
-      <c r="D123" s="169"/>
-      <c r="E123" s="169"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A124" s="169"/>
-      <c r="B124" s="169"/>
-      <c r="C124" s="169"/>
-      <c r="D124" s="169"/>
-      <c r="E124" s="169"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A125" s="169"/>
-      <c r="B125" s="169"/>
-      <c r="C125" s="169"/>
-      <c r="D125" s="169"/>
-      <c r="E125" s="169"/>
+    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="196"/>
+      <c r="B122" s="196"/>
+      <c r="C122" s="196"/>
+      <c r="D122" s="196"/>
+      <c r="E122" s="196"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="196"/>
+      <c r="B123" s="196"/>
+      <c r="C123" s="196"/>
+      <c r="D123" s="196"/>
+      <c r="E123" s="196"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="196"/>
+      <c r="B124" s="196"/>
+      <c r="C124" s="196"/>
+      <c r="D124" s="196"/>
+      <c r="E124" s="196"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="196"/>
+      <c r="B125" s="196"/>
+      <c r="C125" s="196"/>
+      <c r="D125" s="196"/>
+      <c r="E125" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A122:E125"/>
     <mergeCell ref="A116:C117"/>
     <mergeCell ref="A90:E92"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2919,44 +2897,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T37"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" customWidth="1"/>
-    <col min="3" max="3" width="0.36328125" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" customWidth="1"/>
-    <col min="6" max="6" width="12.36328125" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" customWidth="1"/>
-    <col min="9" max="9" width="8.984375E-2" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.36328125" customWidth="1"/>
-    <col min="15" max="15" width="8.984375E-2" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="0.109375" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2981,7 +2959,7 @@
       <c r="N2" s="56"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2997,73 +2975,73 @@
       <c r="M3" s="57"/>
       <c r="N3" s="61"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="181" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="204" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="181" t="s">
+      <c r="D4" s="204" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="185" t="s">
+      <c r="E4" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="181" t="s">
+      <c r="F4" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="189" t="s">
+      <c r="G4" s="206" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="185" t="s">
+      <c r="H4" s="200" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="185" t="s">
+      <c r="I4" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="185" t="s">
+      <c r="J4" s="200" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="192" t="s">
+      <c r="K4" s="209" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="187" t="s">
+      <c r="M4" s="202" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="179" t="s">
+      <c r="N4" s="211" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="131">
         <v>3774269.17</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="183"/>
-      <c r="B5" s="183"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="186"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="193"/>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="205"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="210"/>
       <c r="L5" s="62" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M5" s="188"/>
-      <c r="N5" s="180"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="203"/>
+      <c r="N5" s="212"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65">
         <v>1</v>
       </c>
@@ -3077,7 +3055,7 @@
       <c r="E6" s="75">
         <v>258261.01</v>
       </c>
-      <c r="F6" s="214">
+      <c r="F6" s="186">
         <f t="shared" ref="F6" si="0">E6</f>
         <v>258261.01</v>
       </c>
@@ -3116,7 +3094,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="65">
         <f>A6+1</f>
         <v>2</v>
@@ -3131,7 +3109,7 @@
       <c r="E7" s="75">
         <v>944334.02</v>
       </c>
-      <c r="F7" s="214"/>
+      <c r="F7" s="186"/>
       <c r="G7" s="77">
         <f t="shared" si="1"/>
         <v>944334.02</v>
@@ -3169,22 +3147,22 @@
       </c>
       <c r="P7" s="44"/>
     </row>
-    <row r="8" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="194">
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="167">
         <f t="shared" ref="A8:A23" si="8">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="194" t="s">
+      <c r="B8" s="167" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="195"/>
-      <c r="D8" s="196">
+      <c r="C8" s="168"/>
+      <c r="D8" s="169">
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
         <v>655089.03</v>
       </c>
-      <c r="F8" s="214">
+      <c r="F8" s="186">
         <f>264419.03+380000.03+10670</f>
         <v>655089.06000000006</v>
       </c>
@@ -3224,7 +3202,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="65">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -3239,7 +3217,7 @@
       <c r="E9" s="75">
         <v>259805.04</v>
       </c>
-      <c r="F9" s="214">
+      <c r="F9" s="186">
         <f t="shared" ref="F9:F23" si="10">E9</f>
         <v>259805.04</v>
       </c>
@@ -3280,7 +3258,7 @@
       </c>
       <c r="Q9" s="44"/>
     </row>
-    <row r="10" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -3295,7 +3273,7 @@
       <c r="E10" s="75">
         <v>630064.05000000005</v>
       </c>
-      <c r="F10" s="214"/>
+      <c r="F10" s="186"/>
       <c r="G10" s="77">
         <f t="shared" si="1"/>
         <v>630064.05000000005</v>
@@ -3333,7 +3311,7 @@
       </c>
       <c r="Q10" s="44"/>
     </row>
-    <row r="11" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="65">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -3348,7 +3326,7 @@
       <c r="E11" s="75">
         <v>182597.06</v>
       </c>
-      <c r="F11" s="214">
+      <c r="F11" s="186">
         <f t="shared" si="10"/>
         <v>182597.06</v>
       </c>
@@ -3388,12 +3366,12 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="65">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="214">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="214" t="s">
         <v>62</v>
       </c>
       <c r="C12" s="65"/>
@@ -3403,7 +3381,7 @@
       <c r="E12" s="75">
         <v>676552.07</v>
       </c>
-      <c r="F12" s="214"/>
+      <c r="F12" s="186"/>
       <c r="G12" s="77">
         <f t="shared" si="1"/>
         <v>676552.07</v>
@@ -3440,7 +3418,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="65">
         <f t="shared" si="8"/>
         <v>8</v>
@@ -3455,7 +3433,7 @@
       <c r="E13" s="75">
         <v>225452.08</v>
       </c>
-      <c r="F13" s="214">
+      <c r="F13" s="186">
         <f t="shared" si="10"/>
         <v>225452.08</v>
       </c>
@@ -3498,7 +3476,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65">
         <f t="shared" si="8"/>
         <v>9</v>
@@ -3513,7 +3491,7 @@
       <c r="E14" s="75">
         <v>296093.09000000003</v>
       </c>
-      <c r="F14" s="214">
+      <c r="F14" s="186">
         <f t="shared" si="10"/>
         <v>296093.09000000003</v>
       </c>
@@ -3553,7 +3531,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="65">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -3568,7 +3546,7 @@
       <c r="E15" s="75">
         <v>-181679.9</v>
       </c>
-      <c r="F15" s="214">
+      <c r="F15" s="186">
         <f>RESUMEN!D57</f>
         <v>340000</v>
       </c>
@@ -3608,7 +3586,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -3623,7 +3601,7 @@
       <c r="E16" s="75">
         <v>217341.11</v>
       </c>
-      <c r="F16" s="214">
+      <c r="F16" s="186">
         <f t="shared" si="10"/>
         <v>217341.11</v>
       </c>
@@ -3663,7 +3641,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="65">
         <f t="shared" si="8"/>
         <v>12</v>
@@ -3678,7 +3656,7 @@
       <c r="E17" s="75">
         <v>214252.12</v>
       </c>
-      <c r="F17" s="214">
+      <c r="F17" s="186">
         <f t="shared" si="10"/>
         <v>214252.12</v>
       </c>
@@ -3718,7 +3696,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -3733,7 +3711,7 @@
       <c r="E18" s="75">
         <v>426961.13</v>
       </c>
-      <c r="F18" s="214">
+      <c r="F18" s="186">
         <f t="shared" si="10"/>
         <v>426961.13</v>
       </c>
@@ -3773,7 +3751,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="65">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -3788,7 +3766,7 @@
       <c r="E19" s="75">
         <v>871372.14</v>
       </c>
-      <c r="F19" s="214"/>
+      <c r="F19" s="186"/>
       <c r="G19" s="77">
         <f t="shared" si="1"/>
         <v>871372.14</v>
@@ -3825,23 +3803,23 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="194">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="167">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="B20" s="194" t="s">
+      <c r="B20" s="167" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="196">
+      <c r="C20" s="168"/>
+      <c r="D20" s="169">
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
         <f>4170+65317.15</f>
         <v>69487.149999999994</v>
       </c>
-      <c r="F20" s="214">
+      <c r="F20" s="186">
         <f>59233+10253.82</f>
         <v>69486.820000000007</v>
       </c>
@@ -3881,10 +3859,10 @@
         <v>0.15</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="65">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -3899,7 +3877,7 @@
       <c r="E21" s="75">
         <v>124305.16</v>
       </c>
-      <c r="F21" s="214">
+      <c r="F21" s="186">
         <f t="shared" si="10"/>
         <v>124305.16</v>
       </c>
@@ -3938,15 +3916,15 @@
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
-      <c r="P21" s="197" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q21" s="197"/>
-      <c r="R21" s="197"/>
-      <c r="S21" s="197"/>
-      <c r="T21" s="197"/>
-    </row>
-    <row r="22" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="198" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q21" s="198"/>
+      <c r="R21" s="198"/>
+      <c r="S21" s="198"/>
+      <c r="T21" s="198"/>
+    </row>
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65">
         <f t="shared" si="8"/>
         <v>17</v>
@@ -3961,7 +3939,7 @@
       <c r="E22" s="76">
         <v>421529.17</v>
       </c>
-      <c r="F22" s="214">
+      <c r="F22" s="186">
         <v>0</v>
       </c>
       <c r="G22" s="77">
@@ -3999,13 +3977,13 @@
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="P22" s="197"/>
-      <c r="Q22" s="197"/>
-      <c r="R22" s="197"/>
-      <c r="S22" s="197"/>
-      <c r="T22" s="197"/>
-    </row>
-    <row r="23" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="198"/>
+      <c r="Q22" s="198"/>
+      <c r="R22" s="198"/>
+      <c r="S22" s="198"/>
+      <c r="T22" s="198"/>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="65">
         <f t="shared" si="8"/>
         <v>18</v>
@@ -4020,7 +3998,7 @@
       <c r="E23" s="75">
         <v>165225.18</v>
       </c>
-      <c r="F23" s="214">
+      <c r="F23" s="186">
         <f t="shared" si="10"/>
         <v>165225.18</v>
       </c>
@@ -4059,19 +4037,19 @@
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="P23" s="197"/>
-      <c r="Q23" s="197"/>
-      <c r="R23" s="197"/>
-      <c r="S23" s="197"/>
-      <c r="T23" s="197"/>
-    </row>
-    <row r="24" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="198"/>
+      <c r="Q23" s="198"/>
+      <c r="R23" s="198"/>
+      <c r="S23" s="198"/>
+      <c r="T23" s="198"/>
+    </row>
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65"/>
       <c r="B24" s="65"/>
       <c r="C24" s="66"/>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
-      <c r="F24" s="215"/>
+      <c r="F24" s="187"/>
       <c r="G24" s="77"/>
       <c r="H24" s="77"/>
       <c r="I24" s="78"/>
@@ -4085,7 +4063,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="84"/>
       <c r="B25" s="65"/>
       <c r="C25" s="66"/>
@@ -4102,7 +4080,7 @@
       <c r="N25" s="83"/>
       <c r="O25" s="44"/>
     </row>
-    <row r="26" spans="1:20" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:20" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="84"/>
       <c r="B26" s="67"/>
       <c r="C26" s="66"/>
@@ -4119,7 +4097,7 @@
       <c r="N26" s="83"/>
       <c r="O26" s="44"/>
     </row>
-    <row r="27" spans="1:20" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:20" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="85"/>
       <c r="B27" s="65"/>
       <c r="C27" s="66"/>
@@ -4136,7 +4114,7 @@
       <c r="N27" s="83"/>
       <c r="O27" s="44"/>
     </row>
-    <row r="28" spans="1:20" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="65"/>
       <c r="B28" s="91"/>
       <c r="C28" s="91"/>
@@ -4153,7 +4131,7 @@
       <c r="N28" s="94"/>
       <c r="O28" s="44"/>
     </row>
-    <row r="29" spans="1:20" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="95"/>
       <c r="B29" s="96"/>
       <c r="C29" s="96"/>
@@ -4202,94 +4180,99 @@
         <v>7201743.7100000009</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="51"/>
       <c r="C30" s="51"/>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="169" t="str">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="196" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="169"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="169"/>
-      <c r="F32" s="169"/>
-      <c r="G32" s="169"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="169"/>
-      <c r="J32" s="169"/>
-      <c r="K32" s="169"/>
-      <c r="L32" s="169"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="169"/>
-      <c r="C33" s="169"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="169"/>
-      <c r="F33" s="169"/>
-      <c r="G33" s="169"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="169"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="169"/>
-      <c r="L33" s="169"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="169"/>
-      <c r="C34" s="169"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="169"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="169"/>
-      <c r="J34" s="169"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="169"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="169"/>
-      <c r="C35" s="169"/>
-      <c r="D35" s="169"/>
-      <c r="E35" s="169"/>
-      <c r="F35" s="169"/>
-      <c r="G35" s="169"/>
-      <c r="H35" s="169"/>
-      <c r="I35" s="169"/>
-      <c r="J35" s="169"/>
-      <c r="K35" s="169"/>
-      <c r="L35" s="169"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="169"/>
-      <c r="C36" s="169"/>
-      <c r="D36" s="169"/>
-      <c r="E36" s="169"/>
-      <c r="F36" s="169"/>
-      <c r="G36" s="169"/>
-      <c r="H36" s="169"/>
-      <c r="I36" s="169"/>
-      <c r="J36" s="169"/>
-      <c r="K36" s="169"/>
-      <c r="L36" s="169"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="169"/>
-      <c r="C37" s="169"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="169"/>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="169"/>
-      <c r="I37" s="169"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="169"/>
-      <c r="L37" s="169"/>
+      <c r="C32" s="196"/>
+      <c r="D32" s="196"/>
+      <c r="E32" s="196"/>
+      <c r="F32" s="196"/>
+      <c r="G32" s="196"/>
+      <c r="H32" s="196"/>
+      <c r="I32" s="196"/>
+      <c r="J32" s="196"/>
+      <c r="K32" s="196"/>
+      <c r="L32" s="196"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="196"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="196"/>
+      <c r="E33" s="196"/>
+      <c r="F33" s="196"/>
+      <c r="G33" s="196"/>
+      <c r="H33" s="196"/>
+      <c r="I33" s="196"/>
+      <c r="J33" s="196"/>
+      <c r="K33" s="196"/>
+      <c r="L33" s="196"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="196"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
+      <c r="E34" s="196"/>
+      <c r="F34" s="196"/>
+      <c r="G34" s="196"/>
+      <c r="H34" s="196"/>
+      <c r="I34" s="196"/>
+      <c r="J34" s="196"/>
+      <c r="K34" s="196"/>
+      <c r="L34" s="196"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="196"/>
+      <c r="C35" s="196"/>
+      <c r="D35" s="196"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="196"/>
+      <c r="I35" s="196"/>
+      <c r="J35" s="196"/>
+      <c r="K35" s="196"/>
+      <c r="L35" s="196"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="196"/>
+      <c r="C36" s="196"/>
+      <c r="D36" s="196"/>
+      <c r="E36" s="196"/>
+      <c r="F36" s="196"/>
+      <c r="G36" s="196"/>
+      <c r="H36" s="196"/>
+      <c r="I36" s="196"/>
+      <c r="J36" s="196"/>
+      <c r="K36" s="196"/>
+      <c r="L36" s="196"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="196"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="196"/>
+      <c r="E37" s="196"/>
+      <c r="F37" s="196"/>
+      <c r="G37" s="196"/>
+      <c r="H37" s="196"/>
+      <c r="I37" s="196"/>
+      <c r="J37" s="196"/>
+      <c r="K37" s="196"/>
+      <c r="L37" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="P21:T23"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
@@ -4301,11 +4284,6 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4314,21 +4292,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="C5:K8"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="C3:K8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C5" s="167" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="215"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C8" s="154" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="D8" s="154"/>
       <c r="E8" s="154"/>
@@ -4340,9 +4337,6 @@
       <c r="K8" s="154"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="laurasmiet@gmail.com" xr:uid="{44B2E0B3-0977-4FBD-9355-9C344C7DE166}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>